--- a/HK.xlsx
+++ b/HK.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\A-newWarehouse\FUTU\futu_real\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="80">
   <si>
     <t>币对</t>
   </si>
@@ -235,225 +235,6 @@
   </si>
   <si>
     <t>HK.02433</t>
-  </si>
-  <si>
-    <t>HK.01696</t>
-  </si>
-  <si>
-    <t>HK.01707</t>
-  </si>
-  <si>
-    <t>HK.08118</t>
-  </si>
-  <si>
-    <t>HK.03309</t>
-  </si>
-  <si>
-    <t>HK.08136</t>
-  </si>
-  <si>
-    <t>HK.03319</t>
-  </si>
-  <si>
-    <t>HK.01183</t>
-  </si>
-  <si>
-    <t>HK.02363</t>
-  </si>
-  <si>
-    <t>HK.01598</t>
-  </si>
-  <si>
-    <t>HK.02003</t>
-  </si>
-  <si>
-    <t>HK.08223</t>
-  </si>
-  <si>
-    <t>HK.01765</t>
-  </si>
-  <si>
-    <t>HK.01849</t>
-  </si>
-  <si>
-    <t>HK.01931</t>
-  </si>
-  <si>
-    <t>HK.00382</t>
-  </si>
-  <si>
-    <t>HK.01134</t>
-  </si>
-  <si>
-    <t>HK.03601</t>
-  </si>
-  <si>
-    <t>HK.01895</t>
-  </si>
-  <si>
-    <t>HK.00302</t>
-  </si>
-  <si>
-    <t>HK.01870</t>
-  </si>
-  <si>
-    <t>HK.01691</t>
-  </si>
-  <si>
-    <t>HK.09909</t>
-  </si>
-  <si>
-    <t>HK.08646</t>
-  </si>
-  <si>
-    <t>HK.03390</t>
-  </si>
-  <si>
-    <t>HK.09923</t>
-  </si>
-  <si>
-    <t>HK.08623</t>
-  </si>
-  <si>
-    <t>HK.01163</t>
-  </si>
-  <si>
-    <t>HK.09990</t>
-  </si>
-  <si>
-    <t>HK.09991</t>
-  </si>
-  <si>
-    <t>HK.06989</t>
-  </si>
-  <si>
-    <t>HK.02131</t>
-  </si>
-  <si>
-    <t>HK.06677</t>
-  </si>
-  <si>
-    <t>HK.02158</t>
-  </si>
-  <si>
-    <t>HK.02170</t>
-  </si>
-  <si>
-    <t>HK.02187</t>
-  </si>
-  <si>
-    <t>HK.00606</t>
-  </si>
-  <si>
-    <t>HK.02405</t>
-  </si>
-  <si>
-    <t>HK.02415</t>
-  </si>
-  <si>
-    <t>HK.02487</t>
-  </si>
-  <si>
-    <t>HK.09885</t>
-  </si>
-  <si>
-    <t>HK.03650</t>
-  </si>
-  <si>
-    <t>HK.06060</t>
-  </si>
-  <si>
-    <t>HK.06885</t>
-  </si>
-  <si>
-    <t>HK.02337</t>
-  </si>
-  <si>
-    <t>HK.01697</t>
-  </si>
-  <si>
-    <t>HK.00839</t>
-  </si>
-  <si>
-    <t>HK.02779</t>
-  </si>
-  <si>
-    <t>HK.01916</t>
-  </si>
-  <si>
-    <t>HK.01715</t>
-  </si>
-  <si>
-    <t>HK.03616</t>
-  </si>
-  <si>
-    <t>HK.06162</t>
-  </si>
-  <si>
-    <t>HK.01951</t>
-  </si>
-  <si>
-    <t>HK.06820</t>
-  </si>
-  <si>
-    <t>HK.06110</t>
-  </si>
-  <si>
-    <t>HK.01853</t>
-  </si>
-  <si>
-    <t>HK.06186</t>
-  </si>
-  <si>
-    <t>HK.01756</t>
-  </si>
-  <si>
-    <t>HK.06078</t>
-  </si>
-  <si>
-    <t>HK.01477</t>
-  </si>
-  <si>
-    <t>HK.08659</t>
-  </si>
-  <si>
-    <t>HK.09608</t>
-  </si>
-  <si>
-    <t>HK.01024</t>
-  </si>
-  <si>
-    <t>HK.01413</t>
-  </si>
-  <si>
-    <t>HK.09626</t>
-  </si>
-  <si>
-    <t>HK.09960</t>
-  </si>
-  <si>
-    <t>HK.02251</t>
-  </si>
-  <si>
-    <t>HK.06639</t>
-  </si>
-  <si>
-    <t>HK.02237</t>
-  </si>
-  <si>
-    <t>HK.02407</t>
-  </si>
-  <si>
-    <t>HK.06955</t>
-  </si>
-  <si>
-    <t>HK.02482</t>
-  </si>
-  <si>
-    <t>HK.02439</t>
-  </si>
-  <si>
-    <t>HK.09669</t>
   </si>
   <si>
     <t>参数名</t>
@@ -514,6 +295,7 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
@@ -665,7 +447,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -674,31 +456,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
-        <bgColor rgb="FFF2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -871,27 +641,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="9">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFD9D9D9"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFD9D9D9"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFD9D9D9"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFD9D9D9"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1018,7 +773,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
@@ -1030,134 +785,124 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1469,7 +1214,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D136"/>
+  <dimension ref="A1:D63"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="3"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -1491,24 +1236,24 @@
         <v>4</v>
       </c>
       <c r="B2" s="2">
-        <v>69.555000035</v>
+        <v>0.135849609443359</v>
       </c>
       <c r="C2" s="2">
-        <v>0.069</v>
+        <v>0.0679248047216797</v>
       </c>
       <c r="D2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="4">
-        <v>36</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0.165</v>
+      <c r="B3" s="2">
+        <v>0.28125</v>
+      </c>
+      <c r="C3" s="2">
+        <v>0.140625</v>
       </c>
       <c r="D3" t="s">
         <v>5</v>
@@ -1519,24 +1264,24 @@
         <v>7</v>
       </c>
       <c r="B4" s="2">
-        <v>10.5</v>
+        <v>0.08203125</v>
       </c>
       <c r="C4" s="2">
-        <v>0.055</v>
+        <v>0.041015625</v>
       </c>
       <c r="D4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="4">
-        <v>50</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0.23</v>
+      <c r="B5" s="2">
+        <v>0.390625</v>
+      </c>
+      <c r="C5" s="2">
+        <v>0.1953125</v>
       </c>
       <c r="D5" t="s">
         <v>5</v>
@@ -1547,24 +1292,24 @@
         <v>9</v>
       </c>
       <c r="B6" s="2">
-        <v>10.737999989</v>
+        <v>0.0838906249140625</v>
       </c>
       <c r="C6" s="2">
-        <v>0.069</v>
+        <v>0.0419453124570313</v>
       </c>
       <c r="D6" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="4">
-        <v>19.62</v>
-      </c>
-      <c r="C7" s="4">
-        <v>0.109</v>
+      <c r="B7" s="2">
+        <v>0.15328125</v>
+      </c>
+      <c r="C7" s="2">
+        <v>0.076640625</v>
       </c>
       <c r="D7" t="s">
         <v>5</v>
@@ -1575,24 +1320,24 @@
         <v>11</v>
       </c>
       <c r="B8" s="2">
-        <v>5.802</v>
+        <v>0.045328125</v>
       </c>
       <c r="C8" s="2">
-        <v>0.025</v>
+        <v>0.0226640625</v>
       </c>
       <c r="D8" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:4">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="4">
-        <v>48.5</v>
-      </c>
-      <c r="C9" s="4">
-        <v>0.2</v>
+      <c r="B9" s="2">
+        <v>0.37890625</v>
+      </c>
+      <c r="C9" s="2">
+        <v>0.189453125</v>
       </c>
       <c r="D9" t="s">
         <v>5</v>
@@ -1603,24 +1348,24 @@
         <v>13</v>
       </c>
       <c r="B10" s="2">
-        <v>7.21</v>
+        <v>0.056328125</v>
       </c>
       <c r="C10" s="2">
-        <v>0.036</v>
+        <v>0.0281640625</v>
       </c>
       <c r="D10" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="4">
-        <v>231.5</v>
-      </c>
-      <c r="C11" s="4">
-        <v>1.1</v>
+      <c r="B11" s="2">
+        <v>1.80859375</v>
+      </c>
+      <c r="C11" s="2">
+        <v>0.904296875</v>
       </c>
       <c r="D11" t="s">
         <v>5</v>
@@ -1631,24 +1376,24 @@
         <v>15</v>
       </c>
       <c r="B12" s="2">
-        <v>132</v>
+        <v>1.03125</v>
       </c>
       <c r="C12" s="2">
-        <v>0.72</v>
+        <v>0.515625</v>
       </c>
       <c r="D12" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="4">
-        <v>5.2</v>
-      </c>
-      <c r="C13" s="4">
-        <v>0.051</v>
+      <c r="B13" s="2">
+        <v>0.08125</v>
+      </c>
+      <c r="C13" s="2">
+        <v>0.040625</v>
       </c>
       <c r="D13" t="s">
         <v>5</v>
@@ -1659,24 +1404,24 @@
         <v>17</v>
       </c>
       <c r="B14" s="2">
-        <v>2.6</v>
+        <v>0.040625</v>
       </c>
       <c r="C14" s="2">
-        <v>0.027</v>
+        <v>0.0203125</v>
       </c>
       <c r="D14" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="4">
-        <v>31.6</v>
-      </c>
-      <c r="C15" s="4">
-        <v>0.305</v>
+      <c r="B15" s="2">
+        <v>0.49375</v>
+      </c>
+      <c r="C15" s="2">
+        <v>0.246875</v>
       </c>
       <c r="D15" t="s">
         <v>5</v>
@@ -1687,24 +1432,24 @@
         <v>19</v>
       </c>
       <c r="B16" s="2">
-        <v>4.5</v>
+        <v>0.0703125</v>
       </c>
       <c r="C16" s="2">
-        <v>0.056</v>
+        <v>0.03515625</v>
       </c>
       <c r="D16" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B17" s="4">
-        <v>43.95</v>
-      </c>
-      <c r="C17" s="4">
-        <v>0.4</v>
+      <c r="B17" s="2">
+        <v>0.68671875</v>
+      </c>
+      <c r="C17" s="2">
+        <v>0.343359375</v>
       </c>
       <c r="D17" t="s">
         <v>5</v>
@@ -1715,24 +1460,24 @@
         <v>21</v>
       </c>
       <c r="B18" s="2">
-        <v>97</v>
+        <v>1.515625</v>
       </c>
       <c r="C18" s="2">
-        <v>0.94</v>
+        <v>0.7578125</v>
       </c>
       <c r="D18" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="4">
-        <v>7.2</v>
-      </c>
-      <c r="C19" s="4">
-        <v>0.083</v>
+      <c r="B19" s="2">
+        <v>0.1125</v>
+      </c>
+      <c r="C19" s="2">
+        <v>0.05625</v>
       </c>
       <c r="D19" t="s">
         <v>5</v>
@@ -1743,24 +1488,24 @@
         <v>23</v>
       </c>
       <c r="B20" s="2">
-        <v>5.85</v>
+        <v>0.09140625</v>
       </c>
       <c r="C20" s="2">
-        <v>0.056</v>
+        <v>0.045703125</v>
       </c>
       <c r="D20" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:4">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B21" s="4">
-        <v>27.55</v>
-      </c>
-      <c r="C21" s="4">
-        <v>0.35</v>
+      <c r="B21" s="2">
+        <v>0.43046875</v>
+      </c>
+      <c r="C21" s="2">
+        <v>0.215234375</v>
       </c>
       <c r="D21" t="s">
         <v>5</v>
@@ -1771,24 +1516,24 @@
         <v>25</v>
       </c>
       <c r="B22" s="2">
-        <v>10.287</v>
+        <v>0.160734375</v>
       </c>
       <c r="C22" s="2">
-        <v>0.128</v>
+        <v>0.0803671875</v>
       </c>
       <c r="D22" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:4">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B23" s="4">
-        <v>48.876</v>
-      </c>
-      <c r="C23" s="4">
-        <v>0.55</v>
+      <c r="B23" s="2">
+        <v>0.7636875</v>
+      </c>
+      <c r="C23" s="2">
+        <v>0.38184375</v>
       </c>
       <c r="D23" t="s">
         <v>5</v>
@@ -1799,24 +1544,24 @@
         <v>27</v>
       </c>
       <c r="B24" s="2">
-        <v>111</v>
+        <v>1.734375</v>
       </c>
       <c r="C24" s="2">
-        <v>0.93</v>
+        <v>0.8671875</v>
       </c>
       <c r="D24" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:4">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B25" s="4">
-        <v>10.327083338</v>
-      </c>
-      <c r="C25" s="4">
-        <v>0.199</v>
+      <c r="B25" s="2">
+        <v>0.3227213543125</v>
+      </c>
+      <c r="C25" s="2">
+        <v>0.16136067715625</v>
       </c>
       <c r="D25" t="s">
         <v>5</v>
@@ -1827,24 +1572,24 @@
         <v>29</v>
       </c>
       <c r="B26" s="2">
-        <v>3.195</v>
+        <v>0.09984375</v>
       </c>
       <c r="C26" s="2">
-        <v>0.065</v>
+        <v>0.049921875</v>
       </c>
       <c r="D26" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27" s="3" t="s">
+      <c r="A27" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B27" s="4">
-        <v>5.233333328</v>
-      </c>
-      <c r="C27" s="4">
-        <v>0.085</v>
+      <c r="B27" s="2">
+        <v>0.1635416665</v>
+      </c>
+      <c r="C27" s="2">
+        <v>0.08177083325</v>
       </c>
       <c r="D27" t="s">
         <v>5</v>
@@ -1855,24 +1600,24 @@
         <v>31</v>
       </c>
       <c r="B28" s="2">
-        <v>6.16</v>
+        <v>0.1925</v>
       </c>
       <c r="C28" s="2">
-        <v>0.104</v>
+        <v>0.09625</v>
       </c>
       <c r="D28" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:4">
-      <c r="A29" s="3" t="s">
+      <c r="A29" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B29" s="4">
-        <v>1.526666665</v>
-      </c>
-      <c r="C29" s="4">
-        <v>0.026</v>
+      <c r="B29" s="2">
+        <v>0.04770833328125</v>
+      </c>
+      <c r="C29" s="2">
+        <v>0.023854166640625</v>
       </c>
       <c r="D29" t="s">
         <v>5</v>
@@ -1883,24 +1628,24 @@
         <v>33</v>
       </c>
       <c r="B30" s="2">
-        <v>1.23</v>
+        <v>0.0384375</v>
       </c>
       <c r="C30" s="2">
-        <v>0.02</v>
+        <v>0.01921875</v>
       </c>
       <c r="D30" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="3" t="s">
+      <c r="A31" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B31" s="4">
-        <v>5.824</v>
-      </c>
-      <c r="C31" s="4">
-        <v>0.1084</v>
+      <c r="B31" s="2">
+        <v>0.182</v>
+      </c>
+      <c r="C31" s="2">
+        <v>0.091</v>
       </c>
       <c r="D31" t="s">
         <v>5</v>
@@ -1911,24 +1656,24 @@
         <v>35</v>
       </c>
       <c r="B32" s="2">
-        <v>4.7991</v>
+        <v>0.149971875</v>
       </c>
       <c r="C32" s="2">
-        <v>0.1142</v>
+        <v>0.0749859375</v>
       </c>
       <c r="D32" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="33" spans="1:4">
-      <c r="A33" s="3" t="s">
+      <c r="A33" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B33" s="4">
-        <v>2.681666668</v>
-      </c>
-      <c r="C33" s="4">
-        <v>0.045</v>
+      <c r="B33" s="2">
+        <v>0.083802083375</v>
+      </c>
+      <c r="C33" s="2">
+        <v>0.0419010416875</v>
       </c>
       <c r="D33" t="s">
         <v>5</v>
@@ -1939,24 +1684,24 @@
         <v>37</v>
       </c>
       <c r="B34" s="2">
-        <v>2.900000001</v>
+        <v>0.09062500003125</v>
       </c>
       <c r="C34" s="2">
-        <v>0.057</v>
+        <v>0.045312500015625</v>
       </c>
       <c r="D34" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="35" spans="1:4">
-      <c r="A35" s="3" t="s">
+      <c r="A35" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B35" s="4">
-        <v>3.03</v>
-      </c>
-      <c r="C35" s="4">
-        <v>0.053</v>
+      <c r="B35" s="2">
+        <v>0.0946875</v>
+      </c>
+      <c r="C35" s="2">
+        <v>0.04734375</v>
       </c>
       <c r="D35" t="s">
         <v>5</v>
@@ -1967,24 +1712,24 @@
         <v>39</v>
       </c>
       <c r="B36" s="2">
-        <v>38.74</v>
+        <v>1.210625</v>
       </c>
       <c r="C36" s="2">
-        <v>0.82</v>
+        <v>0.6053125</v>
       </c>
       <c r="D36" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="37" spans="1:4">
-      <c r="A37" s="3" t="s">
+      <c r="A37" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B37" s="4">
-        <v>33.5</v>
-      </c>
-      <c r="C37" s="4">
-        <v>0.955</v>
+      <c r="B37" s="2">
+        <v>1.046875</v>
+      </c>
+      <c r="C37" s="2">
+        <v>0.5234375</v>
       </c>
       <c r="D37" t="s">
         <v>5</v>
@@ -1995,24 +1740,24 @@
         <v>41</v>
       </c>
       <c r="B38" s="2">
-        <v>10.7</v>
+        <v>0.334375</v>
       </c>
       <c r="C38" s="2">
-        <v>0.305</v>
+        <v>0.1671875</v>
       </c>
       <c r="D38" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="39" spans="1:4">
-      <c r="A39" s="3" t="s">
+      <c r="A39" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B39" s="4">
-        <v>9.174583335</v>
-      </c>
-      <c r="C39" s="4">
-        <v>0.184</v>
+      <c r="B39" s="2">
+        <v>0.28670572921875</v>
+      </c>
+      <c r="C39" s="2">
+        <v>0.143352864609375</v>
       </c>
       <c r="D39" t="s">
         <v>5</v>
@@ -2023,24 +1768,24 @@
         <v>43</v>
       </c>
       <c r="B40" s="2">
-        <v>9.04</v>
+        <v>0.2825</v>
       </c>
       <c r="C40" s="2">
-        <v>0.211</v>
+        <v>0.14125</v>
       </c>
       <c r="D40" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="41" spans="1:4">
-      <c r="A41" s="3" t="s">
+      <c r="A41" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B41" s="4">
-        <v>3</v>
-      </c>
-      <c r="C41" s="4">
-        <v>0.06</v>
+      <c r="B41" s="2">
+        <v>0.09375</v>
+      </c>
+      <c r="C41" s="2">
+        <v>0.046875</v>
       </c>
       <c r="D41" t="s">
         <v>5</v>
@@ -2051,24 +1796,24 @@
         <v>45</v>
       </c>
       <c r="B42" s="2">
-        <v>3.549999999</v>
+        <v>0.11093749996875</v>
       </c>
       <c r="C42" s="2">
-        <v>0.075</v>
+        <v>0.055468749984375</v>
       </c>
       <c r="D42" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="43" spans="1:4">
-      <c r="A43" s="3" t="s">
+      <c r="A43" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B43" s="4">
-        <v>10.293333338</v>
-      </c>
-      <c r="C43" s="4">
-        <v>0.195</v>
+      <c r="B43" s="2">
+        <v>0.3216666668125</v>
+      </c>
+      <c r="C43" s="2">
+        <v>0.16083333340625</v>
       </c>
       <c r="D43" t="s">
         <v>5</v>
@@ -2079,24 +1824,24 @@
         <v>47</v>
       </c>
       <c r="B44" s="2">
-        <v>3.365</v>
+        <v>0.10515625</v>
       </c>
       <c r="C44" s="2">
-        <v>0.084</v>
+        <v>0.052578125</v>
       </c>
       <c r="D44" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="45" spans="1:4">
-      <c r="A45" s="3" t="s">
+      <c r="A45" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B45" s="4">
-        <v>38.38</v>
-      </c>
-      <c r="C45" s="4">
-        <v>1.1</v>
+      <c r="B45" s="2">
+        <v>1.199375</v>
+      </c>
+      <c r="C45" s="2">
+        <v>0.5996875</v>
       </c>
       <c r="D45" t="s">
         <v>5</v>
@@ -2107,24 +1852,24 @@
         <v>49</v>
       </c>
       <c r="B46" s="2">
-        <v>4.6</v>
+        <v>0.14375</v>
       </c>
       <c r="C46" s="2">
-        <v>0.106</v>
+        <v>0.071875</v>
       </c>
       <c r="D46" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="47" spans="1:4">
-      <c r="A47" s="3" t="s">
+      <c r="A47" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B47" s="4">
-        <v>10.2094</v>
-      </c>
-      <c r="C47" s="4">
-        <v>0.28</v>
+      <c r="B47" s="2">
+        <v>0.31904375</v>
+      </c>
+      <c r="C47" s="2">
+        <v>0.159521875</v>
       </c>
       <c r="D47" t="s">
         <v>5</v>
@@ -2135,24 +1880,24 @@
         <v>51</v>
       </c>
       <c r="B48" s="2">
-        <v>5.31</v>
+        <v>0.1659375</v>
       </c>
       <c r="C48" s="2">
-        <v>0.084</v>
+        <v>0.08296875</v>
       </c>
       <c r="D48" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="49" spans="1:4">
-      <c r="A49" s="3" t="s">
+      <c r="A49" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B49" s="4">
-        <v>19.124999992</v>
-      </c>
-      <c r="C49" s="4">
-        <v>0.33</v>
+      <c r="B49" s="2">
+        <v>0.59765624975</v>
+      </c>
+      <c r="C49" s="2">
+        <v>0.298828124875</v>
       </c>
       <c r="D49" t="s">
         <v>5</v>
@@ -2163,24 +1908,24 @@
         <v>53</v>
       </c>
       <c r="B50" s="2">
-        <v>60.349</v>
+        <v>1.88590625</v>
       </c>
       <c r="C50" s="2">
-        <v>1.035</v>
+        <v>0.942953125</v>
       </c>
       <c r="D50" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="51" spans="1:4">
-      <c r="A51" s="3" t="s">
+      <c r="A51" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B51" s="4">
-        <v>28.543</v>
-      </c>
-      <c r="C51" s="4">
-        <v>0.599</v>
+      <c r="B51" s="2">
+        <v>0.89196875</v>
+      </c>
+      <c r="C51" s="2">
+        <v>0.445984375</v>
       </c>
       <c r="D51" t="s">
         <v>5</v>
@@ -2191,24 +1936,24 @@
         <v>55</v>
       </c>
       <c r="B52" s="2">
-        <v>3.9745</v>
+        <v>0.124203125</v>
       </c>
       <c r="C52" s="2">
-        <v>0.087</v>
+        <v>0.0621015625</v>
       </c>
       <c r="D52" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="53" spans="1:4">
-      <c r="A53" s="3" t="s">
+      <c r="A53" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B53" s="4">
-        <v>4.72</v>
-      </c>
-      <c r="C53" s="4">
-        <v>0.12</v>
+      <c r="B53" s="2">
+        <v>0.1475</v>
+      </c>
+      <c r="C53" s="2">
+        <v>0.07375</v>
       </c>
       <c r="D53" t="s">
         <v>5</v>
@@ -2219,24 +1964,24 @@
         <v>57</v>
       </c>
       <c r="B54" s="2">
-        <v>10.47399999</v>
+        <v>0.3273124996875</v>
       </c>
       <c r="C54" s="2">
-        <v>0.171</v>
+        <v>0.16365624984375</v>
       </c>
       <c r="D54" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="55" spans="1:4">
-      <c r="A55" s="3" t="s">
+      <c r="A55" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B55" s="4">
-        <v>15.3</v>
-      </c>
-      <c r="C55" s="4">
-        <v>0.26</v>
+      <c r="B55" s="2">
+        <v>0.478125</v>
+      </c>
+      <c r="C55" s="2">
+        <v>0.2390625</v>
       </c>
       <c r="D55" t="s">
         <v>5</v>
@@ -2247,24 +1992,24 @@
         <v>59</v>
       </c>
       <c r="B56" s="2">
-        <v>12.7</v>
+        <v>0.396875</v>
       </c>
       <c r="C56" s="2">
-        <v>0.25</v>
+        <v>0.1984375</v>
       </c>
       <c r="D56" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="57" spans="1:4">
-      <c r="A57" s="3" t="s">
+      <c r="A57" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B57" s="4">
-        <v>7.4</v>
-      </c>
-      <c r="C57" s="4">
-        <v>0.125</v>
+      <c r="B57" s="2">
+        <v>0.23125</v>
+      </c>
+      <c r="C57" s="2">
+        <v>0.115625</v>
       </c>
       <c r="D57" t="s">
         <v>5</v>
@@ -2275,24 +2020,24 @@
         <v>61</v>
       </c>
       <c r="B58" s="2">
-        <v>9.2985</v>
+        <v>0.290578125</v>
       </c>
       <c r="C58" s="2">
-        <v>0.2</v>
+        <v>0.1452890625</v>
       </c>
       <c r="D58" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="59" spans="1:4">
-      <c r="A59" s="3" t="s">
+      <c r="A59" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B59" s="4">
-        <v>75.55</v>
-      </c>
-      <c r="C59" s="4">
-        <v>1.26</v>
+      <c r="B59" s="2">
+        <v>2.3609375</v>
+      </c>
+      <c r="C59" s="2">
+        <v>1.18046875</v>
       </c>
       <c r="D59" t="s">
         <v>5</v>
@@ -2303,24 +2048,24 @@
         <v>63</v>
       </c>
       <c r="B60" s="2">
-        <v>15.07</v>
+        <v>0.4709375</v>
       </c>
       <c r="C60" s="2">
-        <v>0.255</v>
+        <v>0.23546875</v>
       </c>
       <c r="D60" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="61" spans="1:4">
-      <c r="A61" s="3" t="s">
+      <c r="A61" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B61" s="4">
-        <v>18.852</v>
-      </c>
-      <c r="C61" s="4">
-        <v>0.5</v>
+      <c r="B61" s="2">
+        <v>0.589125</v>
+      </c>
+      <c r="C61" s="2">
+        <v>0.2945625</v>
       </c>
       <c r="D61" t="s">
         <v>5</v>
@@ -2331,1048 +2076,26 @@
         <v>65</v>
       </c>
       <c r="B62" s="2">
-        <v>15.04</v>
+        <v>0.47</v>
       </c>
       <c r="C62" s="2">
-        <v>0.32</v>
+        <v>0.235</v>
       </c>
       <c r="D62" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="63" spans="1:4">
-      <c r="A63" s="3" t="s">
+      <c r="A63" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B63" s="4">
-        <v>3.2</v>
-      </c>
-      <c r="C63" s="4">
-        <v>0.053</v>
+      <c r="B63" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="C63" s="2">
+        <v>0.05</v>
       </c>
       <c r="D63" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4">
-      <c r="A64" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B64" s="2">
-        <v>34.221</v>
-      </c>
-      <c r="C64" s="2">
-        <v>1.330999999</v>
-      </c>
-      <c r="D64" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4">
-      <c r="A65" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="B65" s="4">
-        <v>0.82</v>
-      </c>
-      <c r="C65" s="4">
-        <v>0.031</v>
-      </c>
-      <c r="D65" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4">
-      <c r="A66" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B66" s="2">
-        <v>1.07</v>
-      </c>
-      <c r="C66" s="2">
-        <v>0.048</v>
-      </c>
-      <c r="D66" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4">
-      <c r="A67" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="B67" s="4">
-        <v>19.79</v>
-      </c>
-      <c r="C67" s="4">
-        <v>0.83</v>
-      </c>
-      <c r="D67" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4">
-      <c r="A68" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B68" s="2">
-        <v>0.816</v>
-      </c>
-      <c r="C68" s="2">
-        <v>0.028</v>
-      </c>
-      <c r="D68" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4">
-      <c r="A69" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="B69" s="4">
-        <v>47.14894</v>
-      </c>
-      <c r="C69" s="4">
-        <v>1.56</v>
-      </c>
-      <c r="D69" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4">
-      <c r="A70" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="B70" s="2">
-        <v>2.300666664</v>
-      </c>
-      <c r="C70" s="2">
-        <v>0.1</v>
-      </c>
-      <c r="D70" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4">
-      <c r="A71" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="B71" s="4">
-        <v>4.059999991</v>
-      </c>
-      <c r="C71" s="4">
-        <v>0.2</v>
-      </c>
-      <c r="D71" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4">
-      <c r="A72" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B72" s="2">
-        <v>2.1578</v>
-      </c>
-      <c r="C72" s="2">
-        <v>0.096</v>
-      </c>
-      <c r="D72" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4">
-      <c r="A73" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="B73" s="4">
-        <v>21.6</v>
-      </c>
-      <c r="C73" s="4">
-        <v>0.83</v>
-      </c>
-      <c r="D73" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4">
-      <c r="A74" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B74" s="2">
-        <v>3.3</v>
-      </c>
-      <c r="C74" s="2">
-        <v>0.14</v>
-      </c>
-      <c r="D74" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4">
-      <c r="A75" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B75" s="4">
-        <v>3.172492307</v>
-      </c>
-      <c r="C75" s="4">
-        <v>0.108</v>
-      </c>
-      <c r="D75" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4">
-      <c r="A76" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B76" s="2">
-        <v>0.94</v>
-      </c>
-      <c r="C76" s="2">
-        <v>0.044</v>
-      </c>
-      <c r="D76" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4">
-      <c r="A77" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="B77" s="4">
-        <v>12.86</v>
-      </c>
-      <c r="C77" s="4">
-        <v>0.54</v>
-      </c>
-      <c r="D77" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4">
-      <c r="A78" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B78" s="2">
-        <v>9.78</v>
-      </c>
-      <c r="C78" s="2">
-        <v>0.44</v>
-      </c>
-      <c r="D78" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4">
-      <c r="A79" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B79" s="4">
-        <v>4</v>
-      </c>
-      <c r="C79" s="4">
-        <v>0.161</v>
-      </c>
-      <c r="D79" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4">
-      <c r="A80" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B80" s="2">
-        <v>10.96</v>
-      </c>
-      <c r="C80" s="2">
-        <v>0.6</v>
-      </c>
-      <c r="D80" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4">
-      <c r="A81" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="B81" s="4">
-        <v>4.4527</v>
-      </c>
-      <c r="C81" s="4">
-        <v>0.1957</v>
-      </c>
-      <c r="D81" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4">
-      <c r="A82" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="B82" s="2">
-        <v>5.09</v>
-      </c>
-      <c r="C82" s="2">
-        <v>0.163</v>
-      </c>
-      <c r="D82" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4">
-      <c r="A83" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B83" s="4">
-        <v>3.09</v>
-      </c>
-      <c r="C83" s="4">
-        <v>0.105</v>
-      </c>
-      <c r="D83" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4">
-      <c r="A84" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="B84" s="2">
-        <v>25.7849</v>
-      </c>
-      <c r="C84" s="2">
-        <v>0.9908</v>
-      </c>
-      <c r="D84" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4">
-      <c r="A85" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="B85" s="4">
-        <v>30.57</v>
-      </c>
-      <c r="C85" s="4">
-        <v>1.865</v>
-      </c>
-      <c r="D85" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4">
-      <c r="A86" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="B86" s="2">
-        <v>4.12</v>
-      </c>
-      <c r="C86" s="2">
-        <v>0.153</v>
-      </c>
-      <c r="D86" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4">
-      <c r="A87" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="B87" s="4">
-        <v>6.15</v>
-      </c>
-      <c r="C87" s="4">
-        <v>0.218</v>
-      </c>
-      <c r="D87" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4">
-      <c r="A88" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="B88" s="2">
-        <v>122.7</v>
-      </c>
-      <c r="C88" s="2">
-        <v>4.28</v>
-      </c>
-      <c r="D88" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4">
-      <c r="A89" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="B89" s="4">
-        <v>2.770000001</v>
-      </c>
-      <c r="C89" s="4">
-        <v>0.102</v>
-      </c>
-      <c r="D89" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4">
-      <c r="A90" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="B90" s="2">
-        <v>2.52</v>
-      </c>
-      <c r="C90" s="2">
-        <v>0.09</v>
-      </c>
-      <c r="D90" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4">
-      <c r="A91" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="B91" s="4">
-        <v>28.326</v>
-      </c>
-      <c r="C91" s="4">
-        <v>1.05</v>
-      </c>
-      <c r="D91" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4">
-      <c r="A92" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="B92" s="2">
-        <v>148.1</v>
-      </c>
-      <c r="C92" s="2">
-        <v>4.96</v>
-      </c>
-      <c r="D92" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4">
-      <c r="A93" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="B93" s="4">
-        <v>11.0486</v>
-      </c>
-      <c r="C93" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="D93" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4">
-      <c r="A94" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="B94" s="2">
-        <v>12.83</v>
-      </c>
-      <c r="C94" s="2">
-        <v>0.41</v>
-      </c>
-      <c r="D94" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4">
-      <c r="A95" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="B95" s="4">
-        <v>6.4272</v>
-      </c>
-      <c r="C95" s="4">
-        <v>0.2682</v>
-      </c>
-      <c r="D95" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4">
-      <c r="A96" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="B96" s="2">
-        <v>69.76</v>
-      </c>
-      <c r="C96" s="2">
-        <v>2.78</v>
-      </c>
-      <c r="D96" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4">
-      <c r="A97" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="B97" s="4">
-        <v>34.85</v>
-      </c>
-      <c r="C97" s="4">
-        <v>1.23</v>
-      </c>
-      <c r="D97" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4">
-      <c r="A98" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="B98" s="2">
-        <v>10.2</v>
-      </c>
-      <c r="C98" s="2">
-        <v>0.34</v>
-      </c>
-      <c r="D98" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4">
-      <c r="A99" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="B99" s="4">
-        <v>4.5</v>
-      </c>
-      <c r="C99" s="4">
-        <v>0.187</v>
-      </c>
-      <c r="D99" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4">
-      <c r="A100" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="B100" s="2">
-        <v>7.27</v>
-      </c>
-      <c r="C100" s="2">
-        <v>0.285</v>
-      </c>
-      <c r="D100" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4">
-      <c r="A101" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="B101" s="4">
-        <v>13.449</v>
-      </c>
-      <c r="C101" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="D101" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4">
-      <c r="A102" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="B102" s="2">
-        <v>32.6</v>
-      </c>
-      <c r="C102" s="2">
-        <v>1.6</v>
-      </c>
-      <c r="D102" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4">
-      <c r="A103" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="B103" s="4">
-        <v>64.294</v>
-      </c>
-      <c r="C103" s="4">
-        <v>2.96</v>
-      </c>
-      <c r="D103" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4">
-      <c r="A104" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="B104" s="2">
-        <v>42.4</v>
-      </c>
-      <c r="C104" s="2">
-        <v>1.41</v>
-      </c>
-      <c r="D104" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4">
-      <c r="A105" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="B105" s="4">
-        <v>97.8</v>
-      </c>
-      <c r="C105" s="4">
-        <v>8.83</v>
-      </c>
-      <c r="D105" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4">
-      <c r="A106" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="B106" s="2">
-        <v>5.0787</v>
-      </c>
-      <c r="C106" s="2">
-        <v>0.37</v>
-      </c>
-      <c r="D106" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4">
-      <c r="A107" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="B107" s="4">
-        <v>16.0133</v>
-      </c>
-      <c r="C107" s="4">
-        <v>1.02</v>
-      </c>
-      <c r="D107" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4">
-      <c r="A108" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="B108" s="2">
-        <v>2.268144446</v>
-      </c>
-      <c r="C108" s="2">
-        <v>0.223</v>
-      </c>
-      <c r="D108" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4">
-      <c r="A109" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="B109" s="4">
-        <v>19.5798</v>
-      </c>
-      <c r="C109" s="4">
-        <v>1.6</v>
-      </c>
-      <c r="D109" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4">
-      <c r="A110" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="B110" s="2">
-        <v>4.0499</v>
-      </c>
-      <c r="C110" s="2">
-        <v>0.29</v>
-      </c>
-      <c r="D110" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="111" spans="1:4">
-      <c r="A111" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="B111" s="4">
-        <v>6.82553</v>
-      </c>
-      <c r="C111" s="4">
-        <v>0.45927</v>
-      </c>
-      <c r="D111" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="112" spans="1:4">
-      <c r="A112" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="B112" s="2">
-        <v>3.5625</v>
-      </c>
-      <c r="C112" s="2">
-        <v>0.22725</v>
-      </c>
-      <c r="D112" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="113" spans="1:4">
-      <c r="A113" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="B113" s="4">
-        <v>1.67</v>
-      </c>
-      <c r="C113" s="4">
-        <v>0.152</v>
-      </c>
-      <c r="D113" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="114" spans="1:4">
-      <c r="A114" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="B114" s="2">
-        <v>0.66</v>
-      </c>
-      <c r="C114" s="2">
-        <v>0.055</v>
-      </c>
-      <c r="D114" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="115" spans="1:4">
-      <c r="A115" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="B115" s="4">
-        <v>24.3749</v>
-      </c>
-      <c r="C115" s="4">
-        <v>1.92</v>
-      </c>
-      <c r="D115" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="116" spans="1:4">
-      <c r="A116" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="B116" s="2">
-        <v>3.76</v>
-      </c>
-      <c r="C116" s="2">
-        <v>0.33</v>
-      </c>
-      <c r="D116" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="117" spans="1:4">
-      <c r="A117" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="B117" s="4">
-        <v>11.7815</v>
-      </c>
-      <c r="C117" s="4">
-        <v>1.0786</v>
-      </c>
-      <c r="D117" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="118" spans="1:4">
-      <c r="A118" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="B118" s="2">
-        <v>10.4759</v>
-      </c>
-      <c r="C118" s="2">
-        <v>0.82</v>
-      </c>
-      <c r="D118" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="119" spans="1:4">
-      <c r="A119" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="B119" s="4">
-        <v>23.926</v>
-      </c>
-      <c r="C119" s="4">
-        <v>2.6953</v>
-      </c>
-      <c r="D119" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="120" spans="1:4">
-      <c r="A120" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="B120" s="2">
-        <v>3.6629</v>
-      </c>
-      <c r="C120" s="2">
-        <v>0.36</v>
-      </c>
-      <c r="D120" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="121" spans="1:4">
-      <c r="A121" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B121" s="4">
-        <v>109.69233</v>
-      </c>
-      <c r="C121" s="4">
-        <v>8.1</v>
-      </c>
-      <c r="D121" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="122" spans="1:4">
-      <c r="A122" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="B122" s="2">
-        <v>43</v>
-      </c>
-      <c r="C122" s="2">
-        <v>3.62</v>
-      </c>
-      <c r="D122" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="123" spans="1:4">
-      <c r="A123" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="B123" s="4">
-        <v>1.42</v>
-      </c>
-      <c r="C123" s="4">
-        <v>0.095</v>
-      </c>
-      <c r="D123" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="124" spans="1:4">
-      <c r="A124" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="B124" s="2">
-        <v>0.62</v>
-      </c>
-      <c r="C124" s="2">
-        <v>0.039</v>
-      </c>
-      <c r="D124" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="125" spans="1:4">
-      <c r="A125" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="B125" s="4">
-        <v>416.65</v>
-      </c>
-      <c r="C125" s="4">
-        <v>30.6</v>
-      </c>
-      <c r="D125" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="126" spans="1:4">
-      <c r="A126" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="B126" s="2">
-        <v>1.804666667</v>
-      </c>
-      <c r="C126" s="2">
-        <v>0.15</v>
-      </c>
-      <c r="D126" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="127" spans="1:4">
-      <c r="A127" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="B127" s="4">
-        <v>1052</v>
-      </c>
-      <c r="C127" s="4">
-        <v>66.1</v>
-      </c>
-      <c r="D127" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="128" spans="1:4">
-      <c r="A128" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="B128" s="2">
-        <v>9.6328</v>
-      </c>
-      <c r="C128" s="2">
-        <v>0.8112</v>
-      </c>
-      <c r="D128" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="129" spans="1:4">
-      <c r="A129" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="B129" s="4">
-        <v>74.95</v>
-      </c>
-      <c r="C129" s="4">
-        <v>7.87</v>
-      </c>
-      <c r="D129" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="130" spans="1:4">
-      <c r="A130" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="B130" s="2">
-        <v>16.02</v>
-      </c>
-      <c r="C130" s="2">
-        <v>1.59</v>
-      </c>
-      <c r="D130" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="131" spans="1:4">
-      <c r="A131" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="B131" s="4">
-        <v>1.84</v>
-      </c>
-      <c r="C131" s="4">
-        <v>0.18</v>
-      </c>
-      <c r="D131" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="132" spans="1:4">
-      <c r="A132" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="B132" s="2">
-        <v>54.7</v>
-      </c>
-      <c r="C132" s="2">
-        <v>4.345</v>
-      </c>
-      <c r="D132" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="133" spans="1:4">
-      <c r="A133" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="B133" s="4">
-        <v>40</v>
-      </c>
-      <c r="C133" s="4">
-        <v>2.7</v>
-      </c>
-      <c r="D133" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="134" spans="1:4">
-      <c r="A134" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="B134" s="2">
-        <v>2.95</v>
-      </c>
-      <c r="C134" s="2">
-        <v>0.295</v>
-      </c>
-      <c r="D134" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="135" spans="1:4">
-      <c r="A135" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="B135" s="4">
-        <v>2.93</v>
-      </c>
-      <c r="C135" s="4">
-        <v>0.2</v>
-      </c>
-      <c r="D135" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="136" spans="1:4">
-      <c r="A136" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="B136" s="2">
-        <v>29.8</v>
-      </c>
-      <c r="C136" s="2">
-        <v>2.96</v>
-      </c>
-      <c r="D136" t="s">
         <v>5</v>
       </c>
     </row>
@@ -3391,15 +2114,15 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>140</v>
+        <v>67</v>
       </c>
       <c r="B1" t="s">
-        <v>141</v>
+        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>142</v>
+        <v>69</v>
       </c>
       <c r="B2">
         <v>1000000</v>
@@ -3407,7 +2130,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>143</v>
+        <v>70</v>
       </c>
       <c r="B3">
         <v>0.02</v>
@@ -3415,7 +2138,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>144</v>
+        <v>71</v>
       </c>
       <c r="B4">
         <v>7</v>
@@ -3423,7 +2146,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>145</v>
+        <v>72</v>
       </c>
       <c r="B5">
         <v>0.05</v>
@@ -3431,7 +2154,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>146</v>
+        <v>73</v>
       </c>
       <c r="B6">
         <v>0.015</v>
@@ -3439,7 +2162,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>147</v>
+        <v>74</v>
       </c>
       <c r="B7">
         <v>0.01</v>
@@ -3447,7 +2170,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>148</v>
+        <v>75</v>
       </c>
       <c r="B8">
         <v>4</v>
@@ -3455,7 +2178,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>149</v>
+        <v>76</v>
       </c>
       <c r="B9">
         <v>1020</v>
@@ -3463,7 +2186,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>150</v>
+        <v>77</v>
       </c>
       <c r="B10">
         <v>3</v>
@@ -3471,10 +2194,10 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>151</v>
+        <v>78</v>
       </c>
       <c r="B11" t="s">
-        <v>152</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
